--- a/content/Question Bank/Coding Questions/Unit 1 - Introduction to Programming/Unit 1 - Introduction to Programming - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 1 - Introduction to Programming/Unit 1 - Introduction to Programming - Coding Questions.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>The college canteen app greets every student by name the moment they place an order. Write a program that reads a student's name and prints a short greeting confirming that their token number will be called shortly.
-The program must:
-- Read Name.
-- Print the result in exactly the format shown below.
+          <t>It is the lunch-hour rush at the college canteen, and the new ordering app greets every student by name the moment they place an order. Asha has just ordered her plate of samosas, and the screen should reassure her that her token will be called soon.
+Write a program that reads one line containing the student's name and prints a single line: the word `Hello`, then the name exactly as typed, then the fixed phrase `your token number will be called shortly`, all separated by single spaces.
 ### Input Format
 - Line 1: Name
 ### Output Format
 ```
-Hello &lt;Name&gt; your token number will be called shortly
+Hello Asha your token number will be called shortly
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the input line is the name `Asha`. The program stores this name and drops it into the middle of the fixed sentence, printing `Hello Asha your token number will be called shortly`. If the input were `Meena`, only the name in the middle would change.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -789,17 +789,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>The campus gym logs every student who checks in at the entrance. Write a program that reads a student's name and prints a short check-in confirmation.
-The program must:
-- Read Name.
-- Print the result in exactly the format shown below.
+          <t>The campus gym opens at 6 a.m., and a small tablet at the entrance logs every student who walks in. When Rohan taps his ID, the screen should welcome him and confirm that his check-in time has been noted.
+Write a program that reads one line containing the student's name and prints a single line: the words `Welcome to the gym`, then the name exactly as typed, then `check-in time recorded`, separated by single spaces.
 ### Input Format
 - Line 1: Name
 ### Output Format
 ```
-Welcome to the gym &lt;Name&gt; check-in time recorded
+Welcome to the gym Rohan check-in time recorded
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the input is `Rohan`. The program places this name between the two fixed parts of the message and prints `Welcome to the gym Rohan check-in time recorded`. Any other name would appear in exactly the same spot.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -944,19 +944,18 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The hostel allotment system announces every new roommate pairing. Write a program that reads two students' names and prints a line announcing that they are now roommates.
-The program must:
-- Read Name 1.
-- Read Name 2.
-- Print the result in exactly the format shown below.
+          <t>It is hostel allotment day, and the warden's software announces each new roommate pairing on the notice-board screen. Arjun and Vikram have just been assigned to the same room, and the system needs to display that news.
+Write a program that reads two lines - the first student's name, then the second student's name - and prints one line in the form `&lt;Name 1&gt; and &lt;Name 2&gt; are now roommates`.
 ### Input Format
 - Line 1: Name 1
 - Line 2: Name 2
 ### Output Format
 ```
-&lt;Name 1&gt; and &lt;Name 2&gt; are now roommates
+Arjun and Vikram are now roommates
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, line 1 is `Arjun` and line 2 is `Vikram`. The program joins them with the word `and` in the middle and adds `are now roommates` at the end, printing `Arjun and Vikram are now roommates`. The names must appear in the same order they were entered.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -1109,17 +1108,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>The student portal greets every student right after they log in. Write a program that reads a student's name and prints a short welcome-back message.
-The program must:
-- Read Name.
-- Print the result in exactly the format shown below.
+          <t>Rohan opens the student portal to check his assignment marks, types his password, and logs in. The portal greets every returning student by name so the dashboard feels personal.
+Write a program that reads one line containing the student's name and prints a single line: `Welcome back`, then the name exactly as typed, then `you have successfully logged in`, separated by single spaces.
 ### Input Format
 - Line 1: Name
 ### Output Format
 ```
-Welcome back &lt;Name&gt; you have successfully logged in
+Welcome back Rohan you have successfully logged in
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the input is `Rohan`. The program inserts this name right after `Welcome back` and finishes with the fixed phrase, printing `Welcome back Rohan you have successfully logged in`.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -1264,23 +1263,21 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>The college admin office wants a quick preview of a student's ID card before printing it. Write a program that reads a student's name, roll number, and department, then prints them as three clearly labelled lines.
-The program must:
-- Read Name.
-- Read Roll No.
-- Read Department.
-- Print the result in exactly the format shown below.
+          <t>The admin office is printing new student ID cards, and before each card goes to the printer the clerk wants a quick preview on screen. Asha Verma from Computer Science has just submitted her form, so her details need to be shown neatly.
+Write a program that reads three lines - name, roll number, and department - and prints them back as three labelled lines: `Name:`, `Roll No:`, and `Department:`, each label followed by a space and the value exactly as entered.
 ### Input Format
 - Line 1: Name
 - Line 2: Roll No
 - Line 3: Department
 ### Output Format
 ```
-Name: &lt;name&gt;
-Roll No: &lt;roll_no&gt;
-Department: &lt;department&gt;
+Name: Asha Verma
+Roll No: 21CS104
+Department: Computer Science
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the three input lines are `Asha Verma`, `21CS104`, and `Computer Science`. The program attaches the matching label to each value and prints `Name: Asha Verma`, then `Roll No: 21CS104`, then `Department: Computer Science`. The roll number is kept as plain text, so `21CS104` is printed unchanged.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -1457,23 +1454,21 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>The fest registration desk prints a small confirmation slip for every student who signs up for an event. Write a program that reads a student's name, the event, and the day, then prints them as three labelled lines.
-The program must:
-- Read Name.
-- Read Event.
-- Read Day.
-- Print the result in exactly the format shown below.
+          <t>The annual tech fest is on, and the registration desk hands every participant a small confirmation slip. Arjun Mehta has just signed up for the Hackathon on Day 1, and the desk volunteer needs his slip printed.
+Write a program that reads three lines - the student's name, the event, and the day - and prints them as three labelled lines: `Name:`, `Event:`, and `Day:`, each label followed by a space and the value exactly as entered.
 ### Input Format
 - Line 1: Name
 - Line 2: Event
 - Line 3: Day
 ### Output Format
 ```
-Name: &lt;name&gt;
-Event: &lt;event&gt;
-Day: &lt;day&gt;
+Name: Arjun Mehta
+Event: Hackathon
+Day: Day 1
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Arjun Mehta`, `Hackathon`, and `Day 1`. The program pairs each value with its label and prints `Name: Arjun Mehta`, `Event: Hackathon`, and `Day: Day 1` on three separate lines, in that order.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -1650,23 +1645,21 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>The timetable app shows the next class on a student's dashboard. Write a program that reads the subject name, time, and room, then prints them as three labelled lines.
-The program must:
-- Read Subject.
-- Read Time.
-- Read Room.
-- Print the result in exactly the format shown below.
+          <t>The timetable app on every student's phone shows a small card with the next class of the day. Right now it needs to display the upcoming Data Structures lecture so nobody wanders into the wrong room.
+Write a program that reads three lines - the subject, the time, and the room - and prints them as three labelled lines: `Subject:`, `Time:`, and `Room:`, each label followed by a space and the value exactly as entered.
 ### Input Format
 - Line 1: Subject
 - Line 2: Time
 - Line 3: Room
 ### Output Format
 ```
-Subject: &lt;subject&gt;
-Time: &lt;time&gt;
-Room: &lt;room&gt;
+Subject: Data Structures
+Time: 10:00 AM
+Room: 204
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Data Structures`, `10:00 AM`, and `204`. The program prints `Subject: Data Structures`, then `Time: 10:00 AM`, then `Room: 204`. The room number is treated as plain text, so `204` is printed exactly as typed.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -1843,15 +1836,8 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The examination cell generates a hall ticket for every student before the semester exams. Write a program that reads a student's name, roll number, course, semester, exam center, and exam date, then prints the complete hall ticket.
-The program must:
-- Read Name.
-- Read Roll No.
-- Read Course.
-- Read Semester.
-- Read Exam Center.
-- Read Exam Date.
-- Print the result in exactly the format shown below.
+          <t>Semester exams are two weeks away, and the examination cell is generating hall tickets for every registered student. Asha Verma needs hers, complete with her exam centre and date, plus the standard reminder to carry ID proof.
+Write a program that reads six lines - name, roll number, course, semester, exam center, and exam date - and prints an eight-line hall ticket: the heading `EXAM HALL TICKET` on top, the six labelled detail lines in the same order as the input, and the fixed reminder line at the bottom.
 ### Input Format
 - Line 1: Name
 - Line 2: Roll No
@@ -1862,15 +1848,17 @@
 ### Output Format
 ```
 EXAM HALL TICKET
-Name: &lt;name&gt;
-Roll No: &lt;roll_no&gt;
-Course: &lt;course&gt;
-Semester: &lt;semester&gt;
-Exam Center: &lt;exam_center&gt;
-Exam Date: &lt;exam_date&gt;
+Name: Asha Verma
+Roll No: 21CS104
+Course: B.Tech CSE
+Semester: Semester 3
+Exam Center: Block A, Room 12
+Exam Date: 12 Dec 2026
 Carry a valid ID proof to the exam center
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the six inputs are `Asha Verma`, `21CS104`, `B.Tech CSE`, `Semester 3`, `Block A, Room 12`, and `12 Dec 2026`. The program first prints the heading, then each value on its own line after its label (for example `Roll No: 21CS104`), and finally the reminder `Carry a valid ID proof to the exam center`. Every value, including the date, is printed exactly as entered.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -2111,14 +2099,8 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A campus food delivery app prints a slip for every order placed. Write a program that reads the customer's name, the item, the restaurant, the delivery address, and the delivery time, then prints the complete slip.
-The program must:
-- Read Name.
-- Read Item.
-- Read Restaurant.
-- Read Address.
-- Read Delivery Time.
-- Print the result in exactly the format shown below.
+          <t>It is 8 p.m. in the hostel and Rohan Patil has ordered a Paneer Wrap from Campus Bites on the campus food delivery app. For every order, the app prints a slip that the delivery rider clips to the bag.
+Write a program that reads five lines - the customer's name, the item, the restaurant, the delivery address, and the delivery time - and prints a seven-line slip: the heading `FOOD DELIVERY SLIP`, the five labelled detail lines in input order, and the closing line `Your order is on the way`.
 ### Input Format
 - Line 1: Name
 - Line 2: Item
@@ -2128,14 +2110,16 @@
 ### Output Format
 ```
 FOOD DELIVERY SLIP
-Name: &lt;name&gt;
-Item: &lt;item&gt;
-Restaurant: &lt;restaurant&gt;
-Address: &lt;address&gt;
-Delivery Time: &lt;delivery_time&gt;
+Name: Rohan Patil
+Item: Paneer Wrap
+Restaurant: Campus Bites
+Address: Hostel Block B, Room 204
+Delivery Time: 8:30 PM
 Your order is on the way
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the five inputs are `Rohan Patil`, `Paneer Wrap`, `Campus Bites`, `Hostel Block B, Room 204`, and `8:30 PM`. The program prints the heading first, then each value after its label (for example `Item: Paneer Wrap`), and ends with the fixed closing line. The address and time are printed exactly as typed.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
@@ -2360,14 +2344,8 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>The library issues a membership card to every student who registers. Write a program that reads a student's name, member ID, current book, issue date, and due date, then prints the complete card.
-The program must:
-- Read Name.
-- Read Member ID.
-- Read Book.
-- Read Issue Date.
-- Read Due Date.
-- Print the result in exactly the format shown below.
+          <t>Rohan Patil has just registered at the college library, and the librarian's software prints a membership card that also records the book he is borrowing today. The card must list his details along with the issue and due dates, plus the standard return reminder.
+Write a program that reads five lines - name, member ID, book, issue date, and due date - and prints a seven-line card: the heading `LIBRARY MEMBERSHIP CARD`, the five labelled detail lines in input order, and the reminder `Return books on or before the due date`.
 ### Input Format
 - Line 1: Name
 - Line 2: Member ID
@@ -2377,14 +2355,16 @@
 ### Output Format
 ```
 LIBRARY MEMBERSHIP CARD
-Name: &lt;name&gt;
-Member ID: &lt;member_id&gt;
-Book: &lt;book&gt;
-Issue Date: &lt;issue_date&gt;
-Due Date: &lt;due_date&gt;
+Name: Rohan Patil
+Member ID: LIB-2041
+Book: Clean Code
+Issue Date: 20 Jul 2026
+Due Date: 3 Aug 2026
 Return books on or before the due date
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Rohan Patil`, `LIB-2041`, `Clean Code`, `20 Jul 2026`, and `3 Aug 2026`. The program prints the heading, then lines such as `Member ID: LIB-2041` and `Due Date: 3 Aug 2026` in order, and finishes with the reminder line. IDs and dates stay as plain text, printed exactly as entered.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.

--- a/content/Question Bank/Coding Questions/Unit 1 - Introduction to Programming/Unit 1 - Introduction to Programming - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 1 - Introduction to Programming/Unit 1 - Introduction to Programming - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,149 +426,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>difficulty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>bloomTaxonomy</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subjects</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>topics</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>subTopics</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>companies</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>codingType</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>supportAllLanguages</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>enablePartialScore</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ignoreCase</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>testcase1_input</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>testcase1_output</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>testcase2_input</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>testcase2_output</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>testcase3_input</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>testcase3_output</t>
         </is>
@@ -610,29 +585,29 @@
           <t>testcase7_output</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>preloadCode_python</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>solution_python</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>hints</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Canteen Token Greeting</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>It is the lunch-hour rush at the college canteen, and the new ordering app greets every student by name the moment they place an order. Asha has just ordered her plate of samosas, and the screen should reassure her that her token will be called soon.
 Write a program that reads one line containing the student's name and prints a single line: the word `Hello`, then the name exactly as typed, then the fixed phrase `your token number will be called shortly`, all separated by single spaces.
@@ -651,83 +626,89 @@
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" s="2" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Asha</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Hello Asha your token number will be called shortly</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Kabir</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Hello Kabir your token number will be called shortly</t>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Meera</t>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Hello Meera your token number will be called shortly</t>
         </is>
@@ -772,22 +753,20 @@
           <t>Hello S your token number will be called shortly</t>
         </is>
       </c>
-      <c r="AF2" s="3" t="n"/>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>name = input()
 print("Hello", name, "your token number will be called shortly")</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Gym Check-in</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>The campus gym opens at 6 a.m., and a small tablet at the entrance logs every student who walks in. When Rohan taps his ID, the screen should welcome him and confirm that his check-in time has been noted.
 Write a program that reads one line containing the student's name and prints a single line: the words `Welcome to the gym`, then the name exactly as typed, then `check-in time recorded`, separated by single spaces.
@@ -806,83 +785,89 @@
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" s="2" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P3" s="2" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="2" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Rohan</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Welcome to the gym Rohan check-in time recorded</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Welcome to the gym Priya check-in time recorded</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Vikram</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Welcome to the gym Vikram check-in time recorded</t>
         </is>
@@ -927,22 +912,20 @@
           <t>Welcome to the gym S check-in time recorded</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="n"/>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>name = input()
 print("Welcome to the gym", name, "check-in time recorded")</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Roommate Introduction</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>It is hostel allotment day, and the warden's software announces each new roommate pairing on the notice-board screen. Arjun and Vikram have just been assigned to the same room, and the system needs to display that news.
 Write a program that reads two lines - the first student's name, then the second student's name - and prints one line in the form `&lt;Name 1&gt; and &lt;Name 2&gt; are now roommates`.
@@ -962,86 +945,92 @@
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" s="2" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P4" s="2" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q4" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Arjun
 Vikram</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Arjun and Vikram are now roommates</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Divya
 Sneha</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Divya and Sneha are now roommates</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Asha
 Meera</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Asha and Meera are now roommates</t>
         </is>
@@ -1090,23 +1079,21 @@
           <t>S and T are now roommates</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="n"/>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>name1 = input()
 name2 = input()
 print(name1, "and", name2, "are now roommates")</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Login Welcome Message</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Rohan opens the student portal to check his assignment marks, types his password, and logs in. The portal greets every returning student by name so the dashboard feels personal.
 Write a program that reads one line containing the student's name and prints a single line: `Welcome back`, then the name exactly as typed, then `you have successfully logged in`, separated by single spaces.
@@ -1125,83 +1112,89 @@
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" s="2" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P5" s="2" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q5" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Rohan</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Welcome back Rohan you have successfully logged in</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Divya</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Welcome back Divya you have successfully logged in</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Vikram</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Welcome back Vikram you have successfully logged in</t>
         </is>
@@ -1246,22 +1239,20 @@
           <t>Welcome back S you have successfully logged in</t>
         </is>
       </c>
-      <c r="AF5" s="3" t="n"/>
-      <c r="AG5" s="3" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>name = input()
 print("Welcome back", name, "you have successfully logged in")</t>
         </is>
       </c>
-      <c r="AH5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Mini Student ID Card</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>The admin office is printing new student ID cards, and before each card goes to the printer the clerk wants a quick preview on screen. Asha Verma from Computer Science has just submitted her form, so her details need to be shown neatly.
 Write a program that reads three lines - name, roll number, and department - and prints them back as three labelled lines: `Name:`, `Roll No:`, and `Department:`, each label followed by a space and the value exactly as entered.
@@ -1284,93 +1275,99 @@
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" s="2" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P6" s="2" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Asha Verma
 21CS104
 Computer Science</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Name: Asha Verma
 Roll No: 21CS104
 Department: Computer Science</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Kabir Khan
 21EC078
 Electronics</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Name: Kabir Khan
 Roll No: 21EC078
 Department: Electronics</t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Meera Iyer
 21ME032
 Mechanical</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Name: Meera Iyer
 Roll No: 21ME032
@@ -1433,8 +1430,7 @@
 Department: A</t>
         </is>
       </c>
-      <c r="AF6" s="3" t="n"/>
-      <c r="AG6" s="3" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>name = input()
 roll_no = input()
@@ -1444,15 +1440,14 @@
 print("Department:", department)</t>
         </is>
       </c>
-      <c r="AH6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Event Registration Confirmation</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>The annual tech fest is on, and the registration desk hands every participant a small confirmation slip. Arjun Mehta has just signed up for the Hackathon on Day 1, and the desk volunteer needs his slip printed.
 Write a program that reads three lines - the student's name, the event, and the day - and prints them as three labelled lines: `Name:`, `Event:`, and `Day:`, each label followed by a space and the value exactly as entered.
@@ -1475,93 +1470,99 @@
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" s="2" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P7" s="2" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" s="2" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Arjun Mehta
 Hackathon
 Day 1</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Name: Arjun Mehta
 Event: Hackathon
 Day: Day 1</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Divya Shah
 Quiz Night
 Day 2</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Name: Divya Shah
 Event: Quiz Night
 Day: Day 2</t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Vikram Joshi
 Robotics Demo
 Day 1</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Name: Vikram Joshi
 Event: Robotics Demo
@@ -1624,8 +1625,7 @@
 Day: Day 0</t>
         </is>
       </c>
-      <c r="AF7" s="3" t="n"/>
-      <c r="AG7" s="3" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>name = input()
 event = input()
@@ -1635,15 +1635,14 @@
 print("Day:", day)</t>
         </is>
       </c>
-      <c r="AH7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Class Timetable Slot</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>The timetable app on every student's phone shows a small card with the next class of the day. Right now it needs to display the upcoming Data Structures lecture so nobody wanders into the wrong room.
 Write a program that reads three lines - the subject, the time, and the room - and prints them as three labelled lines: `Subject:`, `Time:`, and `Room:`, each label followed by a space and the value exactly as entered.
@@ -1666,93 +1665,99 @@
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" s="2" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P8" s="2" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" s="2" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Data Structures
 10:00 AM
 204</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Subject: Data Structures
 Time: 10:00 AM
 Room: 204</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Operating Systems
 12:00 PM
 118</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Subject: Operating Systems
 Time: 12:00 PM
 Room: 118</t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Python Lab
 2:00 PM
 Lab 3</t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Subject: Python Lab
 Time: 2:00 PM
@@ -1815,8 +1820,7 @@
 Room: A</t>
         </is>
       </c>
-      <c r="AF8" s="3" t="n"/>
-      <c r="AG8" s="3" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>subject = input()
 time = input()
@@ -1826,15 +1830,14 @@
 print("Room:", room)</t>
         </is>
       </c>
-      <c r="AH8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Exam Hall Ticket</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Semester exams are two weeks away, and the examination cell is generating hall tickets for every registered student. Asha Verma needs hers, complete with her exam centre and date, plus the standard reminder to carry ID proof.
 Write a program that reads six lines - name, roll number, course, semester, exam center, and exam date - and prints an eight-line hall ticket: the heading `EXAM HALL TICKET` on top, the six labelled detail lines in the same order as the input, and the fixed reminder line at the bottom.
@@ -1865,58 +1868,64 @@
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" s="2" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P9" s="2" t="b">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q9" s="2" t="b">
+      <c r="Q9" t="b">
         <v>1</v>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Asha Verma
 21CS104
@@ -1926,7 +1935,7 @@
 12 Dec 2026</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>EXAM HALL TICKET
 Name: Asha Verma
@@ -1938,7 +1947,7 @@
 Carry a valid ID proof to the exam center</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Kabir Khan
 21EC078
@@ -1948,7 +1957,7 @@
 12 Dec 2026</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>EXAM HALL TICKET
 Name: Kabir Khan
@@ -1960,7 +1969,7 @@
 Carry a valid ID proof to the exam center</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Meera Iyer
 21ME032
@@ -1970,7 +1979,7 @@
 13 Dec 2026</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>EXAM HALL TICKET
 Name: Meera Iyer
@@ -2070,8 +2079,7 @@
 Carry a valid ID proof to the exam center</t>
         </is>
       </c>
-      <c r="AF9" s="3" t="n"/>
-      <c r="AG9" s="3" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>name = input()
 roll_no = input()
@@ -2089,15 +2097,508 @@
 print("Carry a valid ID proof to the exam center")</t>
         </is>
       </c>
-      <c r="AH9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Lab Welcome Card</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Lab Welcome Card. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+### Output Format
+```
+Welcome Asha to Python lab
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Asha</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Welcome Asha to Python lab</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Welcome Rohan to Python lab</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Meena</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Welcome Meena to Python lab</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Welcome Kabir to Python lab</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Zoya</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Welcome Zoya to Python lab</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Dev Patel</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Welcome Dev Patel to Python lab</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Welcome S to Python lab</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>name=input()
+print("Welcome", name, "to Python lab")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Token Greeting</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Token Greeting. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+### Output Format
+```
+Hello Asha your token is ready
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Asha</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Hello Asha your token is ready</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hello Rohan your token is ready</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Meena</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hello Meena your token is ready</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Hello Kabir your token is ready</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Zoya</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Hello Zoya your token is ready</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Dev Patel</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hello Dev Patel your token is ready</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Hello S your token is ready</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>name=input()
+print("Hello", name, "your token is ready")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Food Delivery Slip</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>It is 8 p.m. in the hostel and Rohan Patil has ordered a Paneer Wrap from Campus Bites on the campus food delivery app. For every order, the app prints a slip that the delivery rider clips to the bag.
 Write a program that reads five lines - the customer's name, the item, the restaurant, the delivery address, and the delivery time - and prints a seven-line slip: the heading `FOOD DELIVERY SLIP`, the five labelled detail lines in input order, and the closing line `Your order is on the way`.
@@ -2126,58 +2627,64 @@
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" s="2" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" s="2" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" s="2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Rohan Patil
 Paneer Wrap
@@ -2186,7 +2693,7 @@
 8:30 PM</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>FOOD DELIVERY SLIP
 Name: Rohan Patil
@@ -2197,7 +2704,7 @@
 Your order is on the way</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Priya Nair
 Veg Biryani
@@ -2206,7 +2713,7 @@
 9:00 PM</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>FOOD DELIVERY SLIP
 Name: Priya Nair
@@ -2217,7 +2724,7 @@
 Your order is on the way</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Sneha Rao
 Masala Maggi
@@ -2226,7 +2733,7 @@
 11:00 PM</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>FOOD DELIVERY SLIP
 Name: Sneha Rao
@@ -2237,7 +2744,7 @@
 Your order is on the way</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Om Prakash
 Chicken Biryani
@@ -2246,7 +2753,7 @@
 10:00 PM</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>FOOD DELIVERY SLIP
 Name: Om Prakash
@@ -2257,7 +2764,7 @@
 Your order is on the way</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Zoya Khan
 Veg Momos
@@ -2266,7 +2773,7 @@
 7:15 PM</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>FOOD DELIVERY SLIP
 Name: Zoya Khan
@@ -2277,7 +2784,7 @@
 Your order is on the way</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Neha Sharma
 Masala Maggi
@@ -2286,7 +2793,7 @@
 12:00 AM</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>FOOD DELIVERY SLIP
 Name: Neha Sharma
@@ -2297,7 +2804,7 @@
 Your order is on the way</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>A
 A
@@ -2306,7 +2813,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>FOOD DELIVERY SLIP
 Name: A
@@ -2317,8 +2824,7 @@
 Your order is on the way</t>
         </is>
       </c>
-      <c r="AF10" s="3" t="n"/>
-      <c r="AG10" s="3" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>name = input()
 item = input()
@@ -2334,15 +2840,14 @@
 print("Your order is on the way")</t>
         </is>
       </c>
-      <c r="AH10" s="2" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Library Membership Card</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Rohan Patil has just registered at the college library, and the librarian's software prints a membership card that also records the book he is borrowing today. The card must list his details along with the issue and due dates, plus the standard return reminder.
 Write a program that reads five lines - name, member ID, book, issue date, and due date - and prints a seven-line card: the heading `LIBRARY MEMBERSHIP CARD`, the five labelled detail lines in input order, and the reminder `Return books on or before the due date`.
@@ -2371,58 +2876,64 @@
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" s="2" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" s="2" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" s="2" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Rohan Patil
 LIB-2041
@@ -2431,7 +2942,7 @@
 3 Aug 2026</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>LIBRARY MEMBERSHIP CARD
 Name: Rohan Patil
@@ -2442,7 +2953,7 @@
 Return books on or before the due date</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Priya Nair
 LIB-2042
@@ -2451,7 +2962,7 @@
 4 Aug 2026</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>LIBRARY MEMBERSHIP CARD
 Name: Priya Nair
@@ -2462,7 +2973,7 @@
 Return books on or before the due date</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Sneha Rao
 LIB-2043
@@ -2471,7 +2982,7 @@
 5 Aug 2026</t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>LIBRARY MEMBERSHIP CARD
 Name: Sneha Rao
@@ -2482,7 +2993,7 @@
 Return books on or before the due date</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Om Prakash
 LIB-2044
@@ -2491,7 +3002,7 @@
 6 Aug 2026</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>LIBRARY MEMBERSHIP CARD
 Name: Om Prakash
@@ -2502,7 +3013,7 @@
 Return books on or before the due date</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Zoya Khan
 LIB-2045
@@ -2511,7 +3022,7 @@
 7 Aug 2026</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>LIBRARY MEMBERSHIP CARD
 Name: Zoya Khan
@@ -2522,7 +3033,7 @@
 Return books on or before the due date</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Neha Sharma
 LIB-2046
@@ -2531,7 +3042,7 @@
 8 Aug 2026</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>LIBRARY MEMBERSHIP CARD
 Name: Neha Sharma
@@ -2542,7 +3053,7 @@
 Return books on or before the due date</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>A
 A
@@ -2551,7 +3062,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>LIBRARY MEMBERSHIP CARD
 Name: A
@@ -2562,8 +3073,7 @@
 Return books on or before the due date</t>
         </is>
       </c>
-      <c r="AF11" s="3" t="n"/>
-      <c r="AG11" s="3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>name = input()
 member_id = input()
@@ -2579,15 +3089,14 @@
 print("Return books on or before the due date")</t>
         </is>
       </c>
-      <c r="AH11" s="2" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Birthday Wish</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A college group chat has a small bot that wishes a student on their birthday. Write a program that reads a student's name and prints a short birthday wish.
 The program must:
@@ -2597,152 +3106,158 @@
 - Line 1: Name
 ### Output Format
 ```
-Happy Birthday &lt;Name&gt; have a great day
+Happy Birthday Meera have a great day
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the input is `Meera`. The bot slots this name into the fixed message and prints `Happy Birthday Meera have a great day`.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" s="2" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" s="2" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q12" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Rohan</t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Happy Birthday Rohan have a great day</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Happy Birthday Priya have a great day</t>
         </is>
       </c>
-      <c r="V12" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Sneha</t>
         </is>
       </c>
-      <c r="W12" s="3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Happy Birthday Sneha have a great day</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Farah</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Happy Birthday Farah have a great day</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Om</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Happy Birthday Om have a great day</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Krishna Reddy</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Happy Birthday Krishna Reddy have a great day</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Happy Birthday T have a great day</t>
         </is>
       </c>
-      <c r="AF12" s="3" t="n"/>
-      <c r="AG12" s="3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>name = input()
 print("Happy Birthday", name, "have a great day")</t>
         </is>
       </c>
-      <c r="AH12" s="2" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Library Borrow Confirmation</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>The college library logs every book that gets borrowed. Write a program that reads a student's name and the title of the book they borrowed, then prints a confirmation line.
 The program must:
@@ -2754,160 +3269,166 @@
 - Line 2: Book Title
 ### Output Format
 ```
-&lt;Name&gt; has borrowed &lt;Book Title&gt; from the library
+Kabir has borrowed The Alchemist from the library
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Kabir` and `The Alchemist`. The program places the name first, then the book title, printing `Kabir has borrowed The Alchemist from the library`.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" s="2" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" s="2" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q13" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Arjun
 Clean Code</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Arjun has borrowed Clean Code from the library</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Divya
 Python Crash Course</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Divya has borrowed Python Crash Course from the library</t>
         </is>
       </c>
-      <c r="V13" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Vikram
 Atomic Habits</t>
         </is>
       </c>
-      <c r="W13" s="3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Vikram has borrowed Atomic Habits from the library</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Neha
 The Alchemist</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Neha has borrowed The Alchemist from the library</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Sameer
 A</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Sameer has borrowed A from the library</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Zoya Khan
 Rich Dad Poor Dad</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Zoya Khan has borrowed Rich Dad Poor Dad from the library</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Om
 Sapiens: A Brief History</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Om has borrowed Sapiens: A Brief History from the library</t>
         </is>
       </c>
-      <c r="AF13" s="3" t="n"/>
-      <c r="AG13" s="3" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>name = input()
 book = input()
 print(name, "has borrowed", book, "from the library")</t>
         </is>
       </c>
-      <c r="AH13" s="2" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Club Membership Confirmation</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Students sign up for college clubs at the start of every semester. Write a program that reads a student's name and the club they joined, then prints a confirmation line.
 The program must:
@@ -2919,160 +3440,166 @@
 - Line 2: Club Name
 ### Output Format
 ```
-&lt;Name&gt; is now a member of the &lt;Club Name&gt; club
+Neha is now a member of the Photography club
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Neha` and `Photography`. The program prints `Neha is now a member of the Photography club`, with the club name slotted in before the word `club`.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" s="2" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" s="2" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Asha
 Photography</t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Asha is now a member of the Photography club</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Kabir
 Coding</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Kabir is now a member of the Coding club</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Meera
 Dance</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Meera is now a member of the Dance club</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Farah
 Debate</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Farah is now a member of the Debate club</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Om
 Music</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Om is now a member of the Music club</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Ananya Gupta
 Robotics</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Ananya Gupta is now a member of the Robotics club</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Dev
 A</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Dev is now a member of the A club</t>
         </is>
       </c>
-      <c r="AF14" s="3" t="n"/>
-      <c r="AG14" s="3" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>name = input()
 club = input()
 print(name, "is now a member of the", club, "club")</t>
         </is>
       </c>
-      <c r="AH14" s="2" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Canteen Receipt Header</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>The canteen's billing screen shows a short header before the full receipt prints. Write a program that reads the item name, token number, and counter number, then prints them as three labelled lines.
 The program must:
@@ -3086,168 +3613,175 @@
 - Line 3: Counter
 ### Output Format
 ```
-Item: &lt;item&gt;
-Token No: &lt;token_no&gt;
-Counter: &lt;counter&gt;
+Item: Veg Puff
+Token No: T-45
+Counter: 2
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Veg Puff`, `T-45`, and `2`. The program prints each value after its matching label — `Item: Veg Puff`, `Token No: T-45`, and `Counter: 2` — in that order.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" s="2" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" s="2" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q15" s="2" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Veg Sandwich
 T-104
 2</t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Item: Veg Sandwich
 Token No: T-104
 Counter: 2</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Cold Coffee
 T-087
 1</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Item: Cold Coffee
 Token No: T-087
 Counter: 1</t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Masala Dosa
 T-156
 3</t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Item: Masala Dosa
 Token No: T-156
 Counter: 3</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Paneer Roll
 T-201
 4</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Item: Paneer Roll
 Token No: T-201
 Counter: 4</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Filter Coffee
 T-002
 1</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Item: Filter Coffee
 Token No: T-002
 Counter: 1</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Idli Sambar
 T-999
 5</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Item: Idli Sambar
 Token No: T-999
 Counter: 5</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>A
 T-1
 0</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Item: A
 Token No: T-1
 Counter: 0</t>
         </is>
       </c>
-      <c r="AF15" s="3" t="n"/>
-      <c r="AG15" s="3" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>item = input()
 token_no = input()
@@ -3257,15 +3791,14 @@
 print("Counter:", counter)</t>
         </is>
       </c>
-      <c r="AH15" s="2" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Hostel Mess Card</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>The hostel mess counter scans a student's mess card before serving food. Write a program that reads a student's name, room number, and mess plan, then prints them as three labelled lines.
 The program must:
@@ -3279,168 +3812,175 @@
 - Line 3: Mess Plan
 ### Output Format
 ```
-Name: &lt;name&gt;
-Room No: &lt;room_no&gt;
-Mess Plan: &lt;mess_plan&gt;
+Name: Aditya
+Room No: B-204
+Mess Plan: Veg Monthly
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Aditya`, `B-204`, and `Veg Monthly`. The program prints `Name: Aditya`, `Room No: B-204`, and `Mess Plan: Veg Monthly`, one label-value pair per line.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" s="2" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" s="2" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q16" s="2" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R16" s="3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Rohan Patil
 B-204
 Veg</t>
         </is>
       </c>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Name: Rohan Patil
 Room No: B-204
 Mess Plan: Veg</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Priya Nair
 G-112
 Non-Veg</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Name: Priya Nair
 Room No: G-112
 Mess Plan: Non-Veg</t>
         </is>
       </c>
-      <c r="V16" s="3" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Sneha Rao
 C-318
 Veg</t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Name: Sneha Rao
 Room No: C-318
 Mess Plan: Veg</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Om Prakash
 A-101
 Jain</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Name: Om Prakash
 Room No: A-101
 Mess Plan: Jain</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Zoya Khan
 D-401
 Non-Veg</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Name: Zoya Khan
 Room No: D-401
 Mess Plan: Non-Veg</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Neha Sharma
 E-002
 Veg</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Name: Neha Sharma
 Room No: E-002
 Mess Plan: Veg</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>S
 B-1
 A</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Name: S
 Room No: B-1
 Mess Plan: A</t>
         </is>
       </c>
-      <c r="AF16" s="3" t="n"/>
-      <c r="AG16" s="3" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>name = input()
 room_no = input()
@@ -3450,15 +3990,14 @@
 print("Mess Plan:", mess_plan)</t>
         </is>
       </c>
-      <c r="AH16" s="2" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Hostel Room Allotment Letter</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>The hostel office sends every new student an allotment letter before the semester begins. Write a program that reads a student's name, room number, block, warden's name, and move-in date, then prints the complete letter.
 The program must:
@@ -3477,72 +4016,80 @@
 ### Output Format
 ```
 HOSTEL ALLOTMENT LETTER
-Name: &lt;name&gt;
-Room No: &lt;room_no&gt;
-Block: &lt;block&gt;
-Warden: &lt;warden&gt;
-Move-in Date: &lt;move-in_date&gt;
+Name: Priya Nair
+Room No: C-112
+Block: C
+Warden: Mr. Suresh
+Move-in Date: 15 Jul 2026
 Report to the warden on the move-in date
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the five inputs are `Priya Nair`, `C-112`, `C`, `Mr. Suresh`, and `15 Jul 2026`. The program prints the heading, then each value after its label such as `Block: C` and `Warden: Mr. Suresh`, and finishes with the fixed reminder line.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" s="2" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" s="2" t="b">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q17" s="2" t="b">
+      <c r="Q9" t="b">
         <v>1</v>
       </c>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Rohan Patil
 G-112
@@ -3551,7 +4098,7 @@
 1 Jul 2026</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>HOSTEL ALLOTMENT LETTER
 Name: Rohan Patil
@@ -3562,7 +4109,7 @@
 Report to the warden on the move-in date</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Priya Nair
 C-318
@@ -3571,7 +4118,7 @@
 2 Jul 2026</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>HOSTEL ALLOTMENT LETTER
 Name: Priya Nair
@@ -3582,7 +4129,7 @@
 Report to the warden on the move-in date</t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Sneha Rao
 B-204
@@ -3591,7 +4138,7 @@
 1 Jul 2026</t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>HOSTEL ALLOTMENT LETTER
 Name: Sneha Rao
@@ -3602,7 +4149,7 @@
 Report to the warden on the move-in date</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Om Prakash
 D-401
@@ -3611,7 +4158,7 @@
 15 Jul 2026</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>HOSTEL ALLOTMENT LETTER
 Name: Om Prakash
@@ -3622,7 +4169,7 @@
 Report to the warden on the move-in date</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Zoya Khan
 E-002
@@ -3631,7 +4178,7 @@
 3 Aug 2026</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>HOSTEL ALLOTMENT LETTER
 Name: Zoya Khan
@@ -3642,7 +4189,7 @@
 Report to the warden on the move-in date</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>Neha Sharma
 A-101
@@ -3651,7 +4198,7 @@
 20 Jul 2026</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>HOSTEL ALLOTMENT LETTER
 Name: Neha Sharma
@@ -3662,7 +4209,7 @@
 Report to the warden on the move-in date</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>S
 A-1
@@ -3671,7 +4218,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>HOSTEL ALLOTMENT LETTER
 Name: S
@@ -3682,8 +4229,7 @@
 Report to the warden on the move-in date</t>
         </is>
       </c>
-      <c r="AF17" s="3" t="n"/>
-      <c r="AG17" s="3" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>name = input()
 room_no = input()
@@ -3699,15 +4245,535 @@
 print("Report to the warden on the move-in date")</t>
         </is>
       </c>
-      <c r="AH17" s="2" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Course Badge</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Course Badge. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+- Line 2: Course
+### Output Format
+```
+Name: Asha
+Course: Python
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Asha
+Python</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Name: Asha
+Course: Python</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Rohan
+DBMS</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Name: Rohan
+Course: DBMS</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Meena
+AI</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Name: Meena
+Course: AI</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Kabir
+Cloud</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Name: Kabir
+Course: Cloud</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Zoya
+Data</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Name: Zoya
+Course: Data</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Dev Patel
+Robotics</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Name: Dev Patel
+Course: Robotics</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>S
+C</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Name: S
+Course: C</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>name=input()
+course=input()
+print("Name:", name)
+print("Course:", course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Study Reminder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Study Reminder. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Subject
+- Line 2: Hours
+### Output Format
+```
+Study Python for 2 hours
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Python
+2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Study Python for 2 hours</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Math
+3</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Study Math for 3 hours</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>DBMS
+1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Study DBMS for 1 hours</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>AI
+4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Study AI for 4 hours</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Cloud
+5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Study Cloud for 5 hours</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Data Science
+6</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Study Data Science for 6 hours</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>C
+0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Study C for 0 hours</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>subject=input()
+hours=input()
+print("Study", subject, "for", hours, "hours")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Movie Ticket Greeting</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>The campus movie-night app confirms every ticket booking with a short message. Write a program that reads a student's name and the movie they booked, then prints a confirmation line.
 The program must:
@@ -3719,160 +4785,166 @@
 - Line 2: Movie
 ### Output Format
 ```
-Enjoy the movie &lt;Name&gt; your ticket for &lt;Movie&gt; is confirmed
+Enjoy the movie Farhan your ticket for Dangal is confirmed
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Farhan` and `Dangal`. The program prints `Enjoy the movie Farhan your ticket for Dangal is confirmed`, inserting the name and movie into their fixed positions.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" s="2" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" s="2" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q18" s="2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Asha
 Interstellar</t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Enjoy the movie Asha your ticket for Interstellar is confirmed</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Kabir
 3 Idiots</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Enjoy the movie Kabir your ticket for 3 Idiots is confirmed</t>
         </is>
       </c>
-      <c r="V18" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Meera
 RRR</t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Enjoy the movie Meera your ticket for RRR is confirmed</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Zoya
 Dune Part Two</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Enjoy the movie Zoya your ticket for Dune Part Two is confirmed</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Om
 KGF</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Enjoy the movie Om your ticket for KGF is confirmed</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Ananya Gupta
 Oppenheimer</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Enjoy the movie Ananya Gupta your ticket for Oppenheimer is confirmed</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>S
 A</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Enjoy the movie S your ticket for A is confirmed</t>
         </is>
       </c>
-      <c r="AF18" s="3" t="n"/>
-      <c r="AG18" s="3" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>name = input()
 movie = input()
 print("Enjoy the movie", name, "your ticket for", movie, "is confirmed")</t>
         </is>
       </c>
-      <c r="AH18" s="2" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - WhatsApp Status Update</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>A group chat bot announces every status update a student posts. Write a program that reads a student's name and their new status text, then prints an announcement line.
 The program must:
@@ -3884,160 +4956,166 @@
 - Line 2: Status
 ### Output Format
 ```
-&lt;Name&gt; updated their status to &lt;Status&gt;
+Simran updated their status to Studying for finals
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Simran` and `Studying for finals`. The program prints `Simran updated their status to Studying for finals`, with the status text appended exactly as typed.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" s="2" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" s="2" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q19" s="2" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R19" s="3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Asha
 Exam week, send help</t>
         </is>
       </c>
-      <c r="S19" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Asha updated their status to Exam week, send help</t>
         </is>
       </c>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Kabir
 Fest mode on</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Kabir updated their status to Fest mode on</t>
         </is>
       </c>
-      <c r="V19" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Meera
 Coffee and code</t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Meera updated their status to Coffee and code</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Om
 Back to hostel life</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Om updated their status to Back to hostel life</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Zoya
 Weekend vibes</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Zoya updated their status to Weekend vibes</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Neha Sharma
 Midterms incoming</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Neha Sharma updated their status to Midterms incoming</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>S
 A</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>S updated their status to A</t>
         </is>
       </c>
-      <c r="AF19" s="3" t="n"/>
-      <c r="AG19" s="3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>name = input()
 status = input()
 print(name, "updated their status to", status)</t>
         </is>
       </c>
-      <c r="AH19" s="2" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Class Rep Announcement</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>The class representative posts short announcements to the class group. Write a program that reads the class rep's name and the announcement message, then prints them as a single announcement line.
 The program must:
@@ -4049,160 +5127,166 @@
 - Line 2: Message
 ### Output Format
 ```
-Class Rep &lt;Name&gt; says &lt;Message&gt;
+Class Rep Devika says Assignment deadline moved to Friday
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Devika` and `Assignment deadline moved to Friday`. The program prints `Class Rep Devika says Assignment deadline moved to Friday`, with the message appearing exactly as entered after the word `says`.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - Input values may contain letters, digits, and spaces only.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" s="2" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" s="2" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q20" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R20" s="3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Kabir
 Submit assignments by Friday</t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Class Rep Kabir says Submit assignments by Friday</t>
         </is>
       </c>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Meera
 Class moved to Room 204</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Class Rep Meera says Class moved to Room 204</t>
         </is>
       </c>
-      <c r="V20" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Asha
 Guest lecture at 2 PM</t>
         </is>
       </c>
-      <c r="W20" s="3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Class Rep Asha says Guest lecture at 2 PM</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Om
 Library closed on Sunday</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Class Rep Om says Library closed on Sunday</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Zoya
 Sports day rescheduled</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Class Rep Zoya says Sports day rescheduled</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Neha Sharma
 Fee submission deadline tomorrow</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Class Rep Neha Sharma says Fee submission deadline tomorrow</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>S
 A</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Class Rep S says A</t>
         </is>
       </c>
-      <c r="AF20" s="3" t="n"/>
-      <c r="AG20" s="3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>name = input()
 message = input()
 print("Class Rep", name, "says", message)</t>
         </is>
       </c>
-      <c r="AH20" s="2" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Library Card</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>The library counter prints a small slip every time a book is issued. Write a program that reads a student's name, the book title, and the due date, then prints them as three labelled lines.
 The program must:
@@ -4216,168 +5300,175 @@
 - Line 3: Due Date
 ### Output Format
 ```
-Name: &lt;name&gt;
-Book: &lt;book&gt;
-Due Date: &lt;due_date&gt;
+Name: Rahul
+Book: Sapiens
+Due Date: 10 Aug 2026
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Rahul`, `Sapiens`, and `10 Aug 2026`. The program prints `Name: Rahul`, `Book: Sapiens`, and `Due Date: 10 Aug 2026`, one per line.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" s="2" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" s="2" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q21" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R21" s="3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Asha Verma
 Clean Code
 20 Jul 2026</t>
         </is>
       </c>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Name: Asha Verma
 Book: Clean Code
 Due Date: 20 Jul 2026</t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Kabir Khan
 Atomic Habits
 22 Jul 2026</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Name: Kabir Khan
 Book: Atomic Habits
 Due Date: 22 Jul 2026</t>
         </is>
       </c>
-      <c r="V21" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Meera Iyer
 Deep Work
 25 Jul 2026</t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Name: Meera Iyer
 Book: Deep Work
 Due Date: 25 Jul 2026</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Om Prakash
 Sapiens
 30 Jul 2026</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Name: Om Prakash
 Book: Sapiens
 Due Date: 30 Jul 2026</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Zoya Khan
 The Alchemist
 1 Aug 2026</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Name: Zoya Khan
 Book: The Alchemist
 Due Date: 1 Aug 2026</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Neha Sharma
 Rich Dad Poor Dad
 5 Aug 2026</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Name: Neha Sharma
 Book: Rich Dad Poor Dad
 Due Date: 5 Aug 2026</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>S
 A
 A</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Name: S
 Book: A
 Due Date: A</t>
         </is>
       </c>
-      <c r="AF21" s="3" t="n"/>
-      <c r="AG21" s="3" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>name = input()
 book = input()
@@ -4387,15 +5478,14 @@
 print("Due Date:", due_date)</t>
         </is>
       </c>
-      <c r="AH21" s="2" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Cab Booking Confirmation</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>The campus cab-sharing app confirms every booking with a short slip. Write a program that reads the passenger's name, the pickup point, and the drop point, then prints them as three labelled lines.
 The program must:
@@ -4409,168 +5499,175 @@
 - Line 3: Drop
 ### Output Format
 ```
-Passenger: &lt;passenger&gt;
-Pickup: &lt;pickup&gt;
-Drop: &lt;drop&gt;
+Passenger: Ishaan
+Pickup: Main Gate
+Drop: Railway Station
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Ishaan`, `Main Gate`, and `Railway Station`. The program prints `Passenger: Ishaan`, `Pickup: Main Gate`, and `Drop: Railway Station`, one per line.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" s="2" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" s="2" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q22" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R22" s="3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Rohan Patil
 Hostel Gate
 Railway Station</t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Passenger: Rohan Patil
 Pickup: Hostel Gate
 Drop: Railway Station</t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Priya Nair
 Main Block
 City Mall</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Passenger: Priya Nair
 Pickup: Main Block
 Drop: City Mall</t>
         </is>
       </c>
-      <c r="V22" s="3" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Sneha Rao
 Library
 Airport</t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Passenger: Sneha Rao
 Pickup: Library
 Drop: Airport</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Om Prakash
 Airport
 City Mall</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Passenger: Om Prakash
 Pickup: Airport
 Drop: City Mall</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Zoya Khan
 Railway Station
 Hostel Gate</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Passenger: Zoya Khan
 Pickup: Railway Station
 Drop: Hostel Gate</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Neha Sharma
 Main Block
 Cinema Hall</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Passenger: Neha Sharma
 Pickup: Main Block
 Drop: Cinema Hall</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>S
 A
 A</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Passenger: S
 Pickup: A
 Drop: A</t>
         </is>
       </c>
-      <c r="AF22" s="3" t="n"/>
-      <c r="AG22" s="3" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>passenger = input()
 pickup = input()
@@ -4580,15 +5677,14 @@
 print("Drop:", drop)</t>
         </is>
       </c>
-      <c r="AH22" s="2" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Online Order Confirmation</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A campus stationery app confirms every order placed by a student. Write a program that reads the item name, quantity, and delivery address, then prints them as three labelled lines. Quantity is read and printed as plain text.
 The program must:
@@ -4602,168 +5698,175 @@
 - Line 3: Deliver To
 ### Output Format
 ```
-Item: &lt;item&gt;
-Quantity: &lt;quantity&gt;
-Deliver To: &lt;deliver_to&gt;
+Item: Notebook Set
+Quantity: 3
+Deliver To: Hostel Block A, Room 12
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the inputs are `Notebook Set`, `3`, and `Hostel Block A, Room 12`. The program prints `Item: Notebook Set`, `Quantity: 3`, and `Deliver To: Hostel Block A, Room 12`. The quantity is kept as plain text, so `3` is printed unchanged.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" s="2" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" s="2" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q23" s="2" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R23" s="3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Notebook Set
 2
 Hostel Block B, Room 204</t>
         </is>
       </c>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Item: Notebook Set
 Quantity: 2
 Deliver To: Hostel Block B, Room 204</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Phone Charger
 1
 Hostel Block C, Room 118</t>
         </is>
       </c>
-      <c r="U23" s="3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Item: Phone Charger
 Quantity: 1
 Deliver To: Hostel Block C, Room 118</t>
         </is>
       </c>
-      <c r="V23" s="3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Sticky Notes
 3
 Hostel Block A, Room 305</t>
         </is>
       </c>
-      <c r="W23" s="3" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Item: Sticky Notes
 Quantity: 3
 Deliver To: Hostel Block A, Room 305</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Highlighter Pack
 5
 Hostel Block D, Room 401</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Item: Highlighter Pack
 Quantity: 5
 Deliver To: Hostel Block D, Room 401</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>USB Drive
 1
 Hostel Block E, Room 2</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Item: USB Drive
 Quantity: 1
 Deliver To: Hostel Block E, Room 2</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Graph Sheets
 10
 Hostel Block A, Room 101</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Item: Graph Sheets
 Quantity: 10
 Deliver To: Hostel Block A, Room 101</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>A
 0
 A</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Item: A
 Quantity: 0
 Deliver To: A</t>
         </is>
       </c>
-      <c r="AF23" s="3" t="n"/>
-      <c r="AG23" s="3" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>item = input()
 quantity = input()
@@ -4773,15 +5876,14 @@
 print("Deliver To:", deliver_to)</t>
         </is>
       </c>
-      <c r="AH23" s="2" t="n"/>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Hostel Visitor Pass</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>The hostel gate issues a short visitor pass for anyone visiting a student. Write a program that reads the visitor's name, the student's name, the room number, and the valid-until time, then prints them as four labelled lines.
 The program must:
@@ -4797,70 +5899,78 @@
 - Line 4: Valid Until
 ### Output Format
 ```
-Visitor Name: &lt;visitor_name&gt;
-Student Name: &lt;student_name&gt;
-Room No: &lt;room_no&gt;
-Valid Until: &lt;valid_until&gt;
+Visitor Name: Anil Kumar
+Student Name: Rohan Patil
+Room No: B-204
+Valid Until: 6:00 PM
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the four inputs are `Anil Kumar`, `Rohan Patil`, `B-204`, and `6:00 PM`. The program prints each value after its matching label, ending with `Valid Until: 6:00 PM`.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" s="2" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" s="2" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q24" s="2" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R24" s="3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Mr. Verma
 Asha Verma
@@ -4868,7 +5978,7 @@
 6:00 PM</t>
         </is>
       </c>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Visitor Name: Mr. Verma
 Student Name: Asha Verma
@@ -4876,7 +5986,7 @@
 Valid Until: 6:00 PM</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Mrs. Khan
 Kabir Khan
@@ -4884,7 +5994,7 @@
 7:00 PM</t>
         </is>
       </c>
-      <c r="U24" s="3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Visitor Name: Mrs. Khan
 Student Name: Kabir Khan
@@ -4892,7 +6002,7 @@
 Valid Until: 7:00 PM</t>
         </is>
       </c>
-      <c r="V24" s="3" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Mr. Iyer
 Meera Iyer
@@ -4900,7 +6010,7 @@
 6:30 PM</t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Visitor Name: Mr. Iyer
 Student Name: Meera Iyer
@@ -4908,7 +6018,7 @@
 Valid Until: 6:30 PM</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Mr. Ansari
 Farah Ansari
@@ -4916,7 +6026,7 @@
 5:00 PM</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Visitor Name: Mr. Ansari
 Student Name: Farah Ansari
@@ -4924,7 +6034,7 @@
 Valid Until: 5:00 PM</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Mrs. Prakash
 Om Prakash
@@ -4932,7 +6042,7 @@
 8:00 PM</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Visitor Name: Mrs. Prakash
 Student Name: Om Prakash
@@ -4940,7 +6050,7 @@
 Valid Until: 8:00 PM</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Mr. Sharma
 Neha Sharma
@@ -4948,7 +6058,7 @@
 6:45 PM</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Visitor Name: Mr. Sharma
 Student Name: Neha Sharma
@@ -4956,7 +6066,7 @@
 Valid Until: 6:45 PM</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>A
 A
@@ -4964,7 +6074,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Visitor Name: A
 Student Name: A
@@ -4972,8 +6082,7 @@
 Valid Until: A</t>
         </is>
       </c>
-      <c r="AF24" s="3" t="n"/>
-      <c r="AG24" s="3" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>visitor_name = input()
 student_name = input()
@@ -4985,15 +6094,725 @@
 print("Valid Until:", valid_until)</t>
         </is>
       </c>
-      <c r="AH24" s="2" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Receipt Header</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Receipt Header. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Stall
+- Line 2: Cashier
+### Output Format
+```
+--- Receipt ---
+Stall: Snacks
+Cashier: Asha
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Snacks
+Asha</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>--- Receipt ---
+Stall: Snacks
+Cashier: Asha</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Juice
+Rohan</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>--- Receipt ---
+Stall: Juice
+Cashier: Rohan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Meals
+Meena</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>--- Receipt ---
+Stall: Meals
+Cashier: Meena</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Tea
+Kabir</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>--- Receipt ---
+Stall: Tea
+Cashier: Kabir</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Bakery
+Zoya</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>--- Receipt ---
+Stall: Bakery
+Cashier: Zoya</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Cafe
+Dev</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>--- Receipt ---
+Stall: Cafe
+Cashier: Dev</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>S
+T</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>--- Receipt ---
+Stall: S
+Cashier: T</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>stall=input()
+cashier=input()
+print("--- Receipt ---")
+print("Stall:", stall)
+print("Cashier:", cashier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Bus Pass Note</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Bus Pass Note. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+- Line 2: Route
+### Output Format
+```
+Bus pass issued to Asha
+Route: R12
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Asha
+R12</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Bus pass issued to Asha
+Route: R12</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Rohan
+B7</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bus pass issued to Rohan
+Route: B7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Meena
+C3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bus pass issued to Meena
+Route: C3</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Kabir
+A1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Bus pass issued to Kabir
+Route: A1</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Zoya
+Z9</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Bus pass issued to Zoya
+Route: Z9</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Dev
+LONG42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bus pass issued to Dev
+Route: LONG42</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>S
+X</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Bus pass issued to S
+Route: X</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>name=input()
+route=input()
+print("Bus pass issued to", name)
+print("Route:", route)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Club Invite</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Club Invite. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+- Line 2: Club
+### Output Format
+```
+Hello Asha
+You are invited to Coding
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Asha
+Coding</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Hello Asha
+You are invited to Coding</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Rohan
+Music</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hello Rohan
+You are invited to Music</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Meena
+Drama</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hello Meena
+You are invited to Drama</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Kabir
+Robotics</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Hello Kabir
+You are invited to Robotics</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Zoya
+Literary</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Hello Zoya
+You are invited to Literary</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Dev
+Eco</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hello Dev
+You are invited to Eco</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>S
+Chess</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Hello S
+You are invited to Chess</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>name=input()
+club=input()
+print("Hello", name)
+print("You are invited to", club)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Internship Confirmation (Mini)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>The placement cell sends a quick confirmation note whenever a student is placed for an internship. Write a program that reads a student's name, the company, the role, and the start date, then prints them as four labelled lines.
 The program must:
@@ -5009,70 +6828,78 @@
 - Line 4: Start Date
 ### Output Format
 ```
-Name: &lt;name&gt;
-Company: &lt;company&gt;
-Role: &lt;role&gt;
-Start Date: &lt;start_date&gt;
+Name: Ananya
+Company: TechNova
+Role: Backend Intern
+Start Date: 1 Sep 2026
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the four inputs are `Ananya`, `TechNova`, `Backend Intern`, and `1 Sep 2026`. The program prints `Name: Ananya`, `Company: TechNova`, `Role: Backend Intern`, and `Start Date: 1 Sep 2026`, one per line.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n"/>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" s="2" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" s="2" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q25" s="2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R25" s="3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Asha Verma
 BrightTech
@@ -5080,7 +6907,7 @@
 1 Aug 2026</t>
         </is>
       </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Name: Asha Verma
 Company: BrightTech
@@ -5088,7 +6915,7 @@
 Start Date: 1 Aug 2026</t>
         </is>
       </c>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Kabir Khan
 NimbusSoft
@@ -5096,7 +6923,7 @@
 5 Aug 2026</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Name: Kabir Khan
 Company: NimbusSoft
@@ -5104,7 +6931,7 @@
 Start Date: 5 Aug 2026</t>
         </is>
       </c>
-      <c r="V25" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Meera Iyer
 Craftly
@@ -5112,7 +6939,7 @@
 10 Aug 2026</t>
         </is>
       </c>
-      <c r="W25" s="3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Name: Meera Iyer
 Company: Craftly
@@ -5120,7 +6947,7 @@
 Start Date: 10 Aug 2026</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Om Prakash
 NextGen Labs
@@ -5128,7 +6955,7 @@
 15 Aug 2026</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Name: Om Prakash
 Company: NextGen Labs
@@ -5136,7 +6963,7 @@
 Start Date: 15 Aug 2026</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Zoya Khan
 QuantumSoft
@@ -5144,7 +6971,7 @@
 20 Aug 2026</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Name: Zoya Khan
 Company: QuantumSoft
@@ -5152,7 +6979,7 @@
 Start Date: 20 Aug 2026</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Neha Sharma
 BrightTech
@@ -5160,7 +6987,7 @@
 1 Sep 2026</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Name: Neha Sharma
 Company: BrightTech
@@ -5168,7 +6995,7 @@
 Start Date: 1 Sep 2026</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>A
 A
@@ -5176,7 +7003,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Name: A
 Company: A
@@ -5184,8 +7011,7 @@
 Start Date: A</t>
         </is>
       </c>
-      <c r="AF25" s="3" t="n"/>
-      <c r="AG25" s="3" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>name = input()
 company = input()
@@ -5197,15 +7023,14 @@
 print("Start Date:", start_date)</t>
         </is>
       </c>
-      <c r="AH25" s="2" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Certificate of Participation</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>The Student Activities Committee prints a certificate for every fest participant. Write a program that reads a student's name, the event, their position, the college name, and the date, then prints the complete certificate.
 The program must:
@@ -5224,72 +7049,80 @@
 ### Output Format
 ```
 CERTIFICATE OF PARTICIPATION
-Name: &lt;name&gt;
-Event: &lt;event&gt;
-Position: &lt;position&gt;
-College: &lt;college&gt;
-Date: &lt;date&gt;
+Name: Vikram Rao
+Event: Coding Marathon
+Position: Runner-up
+College: Sunrise Institute of Technology
+Date: 18 Sep 2026
 Issued by the Student Activities Committee
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the five inputs are `Vikram Rao`, `Coding Marathon`, `Runner-up`, `Sunrise Institute of Technology`, and `18 Sep 2026`. The program prints the heading, then each value after its label such as `Position: Runner-up`, and finally the fixed closing line.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" s="2" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" s="2" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q26" s="2" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Arjun Mehta
 Hackathon 2026
@@ -5298,7 +7131,7 @@
 15 Mar 2026</t>
         </is>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>CERTIFICATE OF PARTICIPATION
 Name: Arjun Mehta
@@ -5309,7 +7142,7 @@
 Issued by the Student Activities Committee</t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Divya Shah
 Quiz Night
@@ -5318,7 +7151,7 @@
 16 Mar 2026</t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>CERTIFICATE OF PARTICIPATION
 Name: Divya Shah
@@ -5329,7 +7162,7 @@
 Issued by the Student Activities Committee</t>
         </is>
       </c>
-      <c r="V26" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Vikram Joshi
 Robotics Demo
@@ -5338,7 +7171,7 @@
 17 Mar 2026</t>
         </is>
       </c>
-      <c r="W26" s="3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>CERTIFICATE OF PARTICIPATION
 Name: Vikram Joshi
@@ -5349,7 +7182,7 @@
 Issued by the Student Activities Committee</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Farah Ansari
 Coding Contest
@@ -5358,7 +7191,7 @@
 18 Mar 2026</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>CERTIFICATE OF PARTICIPATION
 Name: Farah Ansari
@@ -5369,7 +7202,7 @@
 Issued by the Student Activities Committee</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Om Prakash
 Open Mic
@@ -5378,7 +7211,7 @@
 19 Mar 2026</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>CERTIFICATE OF PARTICIPATION
 Name: Om Prakash
@@ -5389,7 +7222,7 @@
 Issued by the Student Activities Committee</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Neha Sharma
 Dance Battle
@@ -5398,7 +7231,7 @@
 20 Mar 2026</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>CERTIFICATE OF PARTICIPATION
 Name: Neha Sharma
@@ -5409,7 +7242,7 @@
 Issued by the Student Activities Committee</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>A
 A
@@ -5418,7 +7251,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>CERTIFICATE OF PARTICIPATION
 Name: A
@@ -5429,8 +7262,7 @@
 Issued by the Student Activities Committee</t>
         </is>
       </c>
-      <c r="AF26" s="3" t="n"/>
-      <c r="AG26" s="3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>name = input()
 event = input()
@@ -5446,15 +7278,14 @@
 print("Issued by the Student Activities Committee")</t>
         </is>
       </c>
-      <c r="AH26" s="2" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - College ID Card</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>The admin office issues a college ID card to every student at the start of the year. Write a program that reads a student's name, roll number, department, year, and blood group, then prints the complete ID card.
 The program must:
@@ -5473,72 +7304,80 @@
 ### Output Format
 ```
 COLLEGE ID CARD
-Name: &lt;name&gt;
-Roll No: &lt;roll_no&gt;
-Department: &lt;department&gt;
-Year: &lt;year&gt;
-Blood Group: &lt;blood_group&gt;
+Name: Sneha Reddy
+Roll No: 22EC031
+Department: Electronics
+Year: 2nd Year
+Blood Group: O+
 This card is non-transferable
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the five inputs are `Sneha Reddy`, `22EC031`, `Electronics`, `2nd Year`, and `O+`. The program prints the heading, then lines such as `Roll No: 22EC031` and `Blood Group: O+` in order, and finishes with the fixed closing line. The roll number stays as plain text, so `22EC031` is printed unchanged.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" s="2" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" s="2" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q27" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Rohan Patil
 21CS104
@@ -5547,7 +7386,7 @@
 B+</t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>COLLEGE ID CARD
 Name: Rohan Patil
@@ -5558,7 +7397,7 @@
 This card is non-transferable</t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Priya Nair
 21EC078
@@ -5567,7 +7406,7 @@
 O+</t>
         </is>
       </c>
-      <c r="U27" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>COLLEGE ID CARD
 Name: Priya Nair
@@ -5578,7 +7417,7 @@
 This card is non-transferable</t>
         </is>
       </c>
-      <c r="V27" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Sneha Rao
 21ME032
@@ -5587,7 +7426,7 @@
 A+</t>
         </is>
       </c>
-      <c r="W27" s="3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>COLLEGE ID CARD
 Name: Sneha Rao
@@ -5598,7 +7437,7 @@
 This card is non-transferable</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Om Prakash
 21EE001
@@ -5607,7 +7446,7 @@
 AB+</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>COLLEGE ID CARD
 Name: Om Prakash
@@ -5618,7 +7457,7 @@
 This card is non-transferable</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Zoya Khan
 21CV009
@@ -5627,7 +7466,7 @@
 O-</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>COLLEGE ID CARD
 Name: Zoya Khan
@@ -5638,7 +7477,7 @@
 This card is non-transferable</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Neha Sharma
 21IT045
@@ -5647,7 +7486,7 @@
 A-</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>COLLEGE ID CARD
 Name: Neha Sharma
@@ -5658,7 +7497,7 @@
 This card is non-transferable</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>A
 A
@@ -5667,7 +7506,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>COLLEGE ID CARD
 Name: A
@@ -5678,8 +7517,7 @@
 This card is non-transferable</t>
         </is>
       </c>
-      <c r="AF27" s="3" t="n"/>
-      <c r="AG27" s="3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>name = input()
 roll_no = input()
@@ -5695,15 +7533,14 @@
 print("This card is non-transferable")</t>
         </is>
       </c>
-      <c r="AH27" s="2" t="n"/>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Canteen Bill Slip</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>The canteen billing counter prints a slip for every order. Write a program that reads the customer's name, the item, the token number, the counter number, and the time, then prints the complete bill slip.
 The program must:
@@ -5722,72 +7559,80 @@
 ### Output Format
 ```
 CANTEEN BILL
-Name: &lt;name&gt;
-Item: &lt;item&gt;
-Token No: &lt;token_no&gt;
-Counter: &lt;counter&gt;
-Time: &lt;time&gt;
+Name: Aisha
+Item: Masala Dosa
+Token No: T-12
+Counter: 1
+Time: 1:15 PM
 Thank you, visit again
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the five inputs are `Aisha`, `Masala Dosa`, `T-12`, `1`, and `1:15 PM`. The program prints the heading, then each value after its label such as `Token No: T-12`, and ends with the fixed closing line.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" s="2" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" s="2" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R28" s="3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Asha Verma
 Veg Thali
@@ -5796,7 +7641,7 @@
 1:15 PM</t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>CANTEEN BILL
 Name: Asha Verma
@@ -5807,7 +7652,7 @@
 Thank you, visit again</t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Kabir Khan
 Cold Coffee
@@ -5816,7 +7661,7 @@
 11:30 AM</t>
         </is>
       </c>
-      <c r="U28" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>CANTEEN BILL
 Name: Kabir Khan
@@ -5827,7 +7672,7 @@
 Thank you, visit again</t>
         </is>
       </c>
-      <c r="V28" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Meera Iyer
 Masala Dosa
@@ -5836,7 +7681,7 @@
 9:45 AM</t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>CANTEEN BILL
 Name: Meera Iyer
@@ -5847,7 +7692,7 @@
 Thank you, visit again</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Om Prakash
 Filter Coffee
@@ -5856,7 +7701,7 @@
 8:00 AM</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>CANTEEN BILL
 Name: Om Prakash
@@ -5867,7 +7712,7 @@
 Thank you, visit again</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Zoya Khan
 Paneer Roll
@@ -5876,7 +7721,7 @@
 2:30 PM</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>CANTEEN BILL
 Name: Zoya Khan
@@ -5887,7 +7732,7 @@
 Thank you, visit again</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Neha Sharma
 Idli Sambar
@@ -5896,7 +7741,7 @@
 7:00 AM</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>CANTEEN BILL
 Name: Neha Sharma
@@ -5907,7 +7752,7 @@
 Thank you, visit again</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>A
 A
@@ -5916,7 +7761,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>CANTEEN BILL
 Name: A
@@ -5927,8 +7772,7 @@
 Thank you, visit again</t>
         </is>
       </c>
-      <c r="AF28" s="3" t="n"/>
-      <c r="AG28" s="3" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>name = input()
 item = input()
@@ -5944,15 +7788,14 @@
 print("Thank you, visit again")</t>
         </is>
       </c>
-      <c r="AH28" s="2" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Cab Trip Receipt</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>A campus cab-sharing app prints a receipt at the end of every trip. Write a program that reads the passenger's name, the pickup point, the drop point, the driver's name, and the fare, then prints the complete receipt. Fare is read and printed as plain text.
 The program must:
@@ -5971,72 +7814,80 @@
 ### Output Format
 ```
 CAB TRIP RECEIPT
-Name: &lt;name&gt;
-Pickup: &lt;pickup&gt;
-Drop: &lt;drop&gt;
-Driver: &lt;driver&gt;
-Fare: &lt;fare&gt;
+Name: Manav
+Pickup: Hostel Gate
+Drop: City Mall
+Driver: Ramesh
+Fare: 180
 Thank you for riding with us
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the five inputs are `Manav`, `Hostel Gate`, `City Mall`, `Ramesh`, and `180`. The program prints the heading, then each value after its label, ending with the fixed closing line. The fare is kept as plain text, so `180` is printed unchanged.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" s="2" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" s="2" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q29" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R29" s="3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Arjun Mehta
 Hostel Gate
@@ -6045,7 +7896,7 @@
 180</t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>CAB TRIP RECEIPT
 Name: Arjun Mehta
@@ -6056,7 +7907,7 @@
 Thank you for riding with us</t>
         </is>
       </c>
-      <c r="T29" s="3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Divya Shah
 Main Block
@@ -6065,7 +7916,7 @@
 120</t>
         </is>
       </c>
-      <c r="U29" s="3" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>CAB TRIP RECEIPT
 Name: Divya Shah
@@ -6076,7 +7927,7 @@
 Thank you for riding with us</t>
         </is>
       </c>
-      <c r="V29" s="3" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Vikram Joshi
 Library
@@ -6085,7 +7936,7 @@
 450</t>
         </is>
       </c>
-      <c r="W29" s="3" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>CAB TRIP RECEIPT
 Name: Vikram Joshi
@@ -6096,7 +7947,7 @@
 Thank you for riding with us</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Om Prakash
 Airport
@@ -6105,7 +7956,7 @@
 300</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>CAB TRIP RECEIPT
 Name: Om Prakash
@@ -6116,7 +7967,7 @@
 Thank you for riding with us</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Zoya Khan
 Main Block
@@ -6125,7 +7976,7 @@
 90</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>CAB TRIP RECEIPT
 Name: Zoya Khan
@@ -6136,7 +7987,7 @@
 Thank you for riding with us</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Neha Sharma
 Hostel Gate
@@ -6145,7 +7996,7 @@
 60</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>CAB TRIP RECEIPT
 Name: Neha Sharma
@@ -6156,7 +8007,7 @@
 Thank you for riding with us</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>A
 A
@@ -6165,7 +8016,7 @@
 0</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>CAB TRIP RECEIPT
 Name: A
@@ -6176,8 +8027,7 @@
 Thank you for riding with us</t>
         </is>
       </c>
-      <c r="AF29" s="3" t="n"/>
-      <c r="AG29" s="3" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>name = input()
 pickup = input()
@@ -6193,15 +8043,14 @@
 print("Thank you for riding with us")</t>
         </is>
       </c>
-      <c r="AH29" s="2" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Internship Offer Snippet</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>The placement cell prints a short offer snippet for every student placed in an internship. Write a program that reads a student's name, the company, the role, the start date, and the stipend, then prints the complete offer snippet. Stipend is read and printed as plain text.
 The program must:
@@ -6220,72 +8069,80 @@
 ### Output Format
 ```
 INTERNSHIP OFFER
-Name: &lt;name&gt;
-Company: &lt;company&gt;
-Role: &lt;role&gt;
-Start Date: &lt;start_date&gt;
-Stipend: &lt;stipend&gt;
+Name: Kavya
+Company: Nimbus Labs
+Role: Data Analyst Intern
+Start Date: 5 Oct 2026
+Stipend: 15000
 Please confirm your acceptance by email
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the five inputs are `Kavya`, `Nimbus Labs`, `Data Analyst Intern`, `5 Oct 2026`, and `15000`. The program prints the heading, then each value after its label such as `Stipend: 15000`, and ends with the fixed closing line. The stipend is kept as plain text, so it is printed exactly as entered.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" s="2" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" s="2" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" s="2" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R30" s="3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Asha Verma
 BrightTech
@@ -6294,7 +8151,7 @@
 15000</t>
         </is>
       </c>
-      <c r="S30" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>INTERNSHIP OFFER
 Name: Asha Verma
@@ -6305,7 +8162,7 @@
 Please confirm your acceptance by email</t>
         </is>
       </c>
-      <c r="T30" s="3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Kabir Khan
 NimbusSoft
@@ -6314,7 +8171,7 @@
 12000</t>
         </is>
       </c>
-      <c r="U30" s="3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>INTERNSHIP OFFER
 Name: Kabir Khan
@@ -6325,7 +8182,7 @@
 Please confirm your acceptance by email</t>
         </is>
       </c>
-      <c r="V30" s="3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Meera Iyer
 Craftly
@@ -6334,7 +8191,7 @@
 10000</t>
         </is>
       </c>
-      <c r="W30" s="3" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>INTERNSHIP OFFER
 Name: Meera Iyer
@@ -6345,7 +8202,7 @@
 Please confirm your acceptance by email</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Om Prakash
 NextGen Labs
@@ -6354,7 +8211,7 @@
 18000</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>INTERNSHIP OFFER
 Name: Om Prakash
@@ -6365,7 +8222,7 @@
 Please confirm your acceptance by email</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Zoya Khan
 QuantumSoft
@@ -6374,7 +8231,7 @@
 9000</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>INTERNSHIP OFFER
 Name: Zoya Khan
@@ -6385,7 +8242,7 @@
 Please confirm your acceptance by email</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Neha Sharma
 BrightTech
@@ -6394,7 +8251,7 @@
 0</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>INTERNSHIP OFFER
 Name: Neha Sharma
@@ -6405,7 +8262,7 @@
 Please confirm your acceptance by email</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>A
 A
@@ -6414,7 +8271,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>INTERNSHIP OFFER
 Name: A
@@ -6425,8 +8282,7 @@
 Please confirm your acceptance by email</t>
         </is>
       </c>
-      <c r="AF30" s="3" t="n"/>
-      <c r="AG30" s="3" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>name = input()
 company = input()
@@ -6442,15 +8298,14 @@
 print("Please confirm your acceptance by email")</t>
         </is>
       </c>
-      <c r="AH30" s="2" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Class Representative Announcement</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>The class representative posts a formal announcement to the class group on important days. Write a program that reads the class rep's name, the class, the message, the date, and the time, then prints the complete announcement.
 The program must:
@@ -6469,72 +8324,80 @@
 ### Output Format
 ```
 ANNOUNCEMENT
-Name: &lt;name&gt;
-Class: &lt;class&gt;
-Message: &lt;message&gt;
-Date: &lt;date&gt;
-Time: &lt;time&gt;
+Name: Devika
+Class: CSE-B
+Message: Guest lecture at 4 PM in Seminar Hall
+Date: 22 Sep 2026
+Time: 4:00 PM
 - Class Representative
 ```
 Every value must be printed exactly as entered, with no extra text added or removed.
+### Example Walkthrough
+In the sample, the five inputs are `Devika`, `CSE-B`, `Guest lecture at 4 PM in Seminar Hall`, `22 Sep 2026`, and `4:00 PM`. The program prints the heading, then each value after its label such as `Class: CSE-B`, and ends with the fixed signature line `- Class Representative`.
 ### Constraints
 - Every input value is a non-empty single line of text.
 - No input value exceeds 40 characters.
 - ID-like fields (roll numbers, token numbers, dates, etc.) are read and printed as plain text, never as numbers.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" s="2" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" s="2" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q31" s="2" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R31" s="3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Kabir Khan
 B.Tech CSE - Sem 3
@@ -6543,7 +8406,7 @@
 5:00 PM</t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>ANNOUNCEMENT
 Name: Kabir Khan
@@ -6554,7 +8417,7 @@
 - Class Representative</t>
         </is>
       </c>
-      <c r="T31" s="3" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Meera Iyer
 B.Tech ECE - Sem 3
@@ -6563,7 +8426,7 @@
 9:00 AM</t>
         </is>
       </c>
-      <c r="U31" s="3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>ANNOUNCEMENT
 Name: Meera Iyer
@@ -6574,7 +8437,7 @@
 - Class Representative</t>
         </is>
       </c>
-      <c r="V31" s="3" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Asha Verma
 B.Tech ME - Sem 3
@@ -6583,7 +8446,7 @@
 2:00 PM</t>
         </is>
       </c>
-      <c r="W31" s="3" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>ANNOUNCEMENT
 Name: Asha Verma
@@ -6594,7 +8457,7 @@
 - Class Representative</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Farah Ansari
 B.Tech CSE - Sem 5
@@ -6603,7 +8466,7 @@
 10:00 AM</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>ANNOUNCEMENT
 Name: Farah Ansari
@@ -6614,7 +8477,7 @@
 - Class Representative</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Om Prakash
 B.Tech EEE - Sem 1
@@ -6623,7 +8486,7 @@
 9:00 AM</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>ANNOUNCEMENT
 Name: Om Prakash
@@ -6634,7 +8497,7 @@
 - Class Representative</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Neha Sharma
 B.Tech IT - Sem 7
@@ -6643,7 +8506,7 @@
 11:59 PM</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>ANNOUNCEMENT
 Name: Neha Sharma
@@ -6654,7 +8517,7 @@
 - Class Representative</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>A
 A
@@ -6663,7 +8526,7 @@
 A</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>ANNOUNCEMENT
 Name: A
@@ -6674,8 +8537,7 @@
 - Class Representative</t>
         </is>
       </c>
-      <c r="AF31" s="3" t="n"/>
-      <c r="AG31" s="3" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>name = input()
 class_name = input()
@@ -6691,7 +8553,585 @@
 print("- Class Representative")</t>
         </is>
       </c>
-      <c r="AH31" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Library Slip</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Library Slip. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+- Line 2: Book
+- Line 3: Due
+### Output Format
+```
+Student: Asha
+Book: Python 101
+Due: Friday
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Asha
+Python 101
+Friday</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Student: Asha
+Book: Python 101
+Due: Friday</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Rohan
+Data
+Monday</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Student: Rohan
+Book: Data
+Due: Monday</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Meena
+Algorithms
+Tuesday</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Student: Meena
+Book: Algorithms
+Due: Tuesday</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Kabir
+Clean Code
+30 July</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Student: Kabir
+Book: Clean Code
+Due: 30 July</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Zoya
+AI Today
+Tomorrow</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Student: Zoya
+Book: AI Today
+Due: Tomorrow</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Dev
+Learning Python
+2026-08-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Student: Dev
+Book: Learning Python
+Due: 2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>S
+B
+D</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Student: S
+Book: B
+Due: D</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>student=input()
+book=input()
+due=input()
+print("Student:", student)
+print("Book:", book)
+print("Due:", due)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Event Seat Card</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Event Seat Card. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+- Line 2: Event
+- Line 3: Seat
+### Output Format
+```
+Event: Tech Talk
+Seat: A12
+Guest: Asha
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Asha
+Tech Talk
+A12</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Event: Tech Talk
+Seat: A12
+Guest: Asha</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Rohan
+Quiz
+B7</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Event: Quiz
+Seat: B7
+Guest: Rohan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Meena
+Dance
+C3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Event: Dance
+Seat: C3
+Guest: Meena</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Kabir
+Hackathon
+H1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Event: Hackathon
+Seat: H1
+Guest: Kabir</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Zoya
+Debate
+D9</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Event: Debate
+Seat: D9
+Guest: Zoya</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Dev
+Bootcamp
+P20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Event: Bootcamp
+Seat: P20
+Guest: Dev</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>S
+E
+1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Event: E
+Seat: 1
+Guest: S</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>name=input()
+event=input()
+seat=input()
+print("Event:", event)
+print("Seat:", seat)
+print("Guest:", name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Mini Profile</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Mini Profile. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+- Line 2: City
+- Line 3: Hobby
+### Output Format
+```
+Profile
+Name: Asha
+City: Hyderabad
+Hobby: Reading
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>introduction-to-programming</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>python-environment</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Asha
+Hyderabad
+Reading</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Profile
+Name: Asha
+City: Hyderabad
+Hobby: Reading</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Rohan
+Pune
+Cricket</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Profile
+Name: Rohan
+City: Pune
+Hobby: Cricket</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Meena
+Delhi
+Music</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Profile
+Name: Meena
+City: Delhi
+Hobby: Music</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Kabir
+Chennai
+Coding</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Profile
+Name: Kabir
+City: Chennai
+Hobby: Coding</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Zoya
+Mumbai
+Art</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Profile
+Name: Zoya
+City: Mumbai
+Hobby: Art</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Dev
+Bengaluru
+Robotics</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Profile
+Name: Dev
+City: Bengaluru
+Hobby: Robotics</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>S
+X
+Y</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Profile
+Name: S
+City: X
+Hobby: Y</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>name=input()
+city=input()
+hobby=input()
+print("Profile")
+print("Name:", name)
+print("City:", city)
+print("Hobby:", hobby)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
